--- a/LubanConfig/Moba/Production/Datas/J-标签表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-标签表.xlsx
@@ -5054,52 +5054,52 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>激活必需标签定义 ID 列表，逗号分隔。</t>
+          <t>激活前必须全部具备的标签 ID；与激活规则组同时配置时两者都要满足。空表示无此要求。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>激活阻断标签定义 ID 列表，逗号分隔。</t>
+          <t>激活前任一命中即阻断的标签 ID；简单 OR 条件优先填此列。空表示无此阻断。</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>应用标签定义 ID 列表，逗号分隔。</t>
+          <t>持续对象处于生效状态时授予的事实标签 ID；暂停或结束后不再授予。空表示只配置门禁。</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>移除必需标签定义 ID 列表，逗号分隔。</t>
+          <t>持续期间全部具备时触发移除的标签 ID；与移除规则组同时配置时两者都要满足。</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>移除阻断标签定义 ID 列表，逗号分隔。</t>
+          <t>持续期间这些标签全部不存在时才满足移除条件；不是“遇到这些标签就移除”。</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>持续中必需标签定义 ID 列表，逗号分隔。</t>
+          <t>持续期间必须全部具备的标签 ID；不满足时暂停，恢复后继续。空表示无此要求。</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>持续中阻断标签定义 ID 列表，逗号分隔。</t>
+          <t>持续期间任一命中即暂停的标签 ID；标签消失后可恢复。空表示无此阻断。</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>激活条件规则组 ID；0 表示不使用。</t>
+          <t>复合激活条件规则组 ID；与平铺条件按 AND 合并。简单 Required/Blocked 优先使用标签列；0 表示不使用。</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>移除条件规则组 ID；0 表示不使用。</t>
+          <t>复合移除条件规则组 ID；与平铺条件按 AND 合并。整组留空时不会自动移除；0 表示不使用。</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>持续中条件规则组 ID；0 表示不使用。</t>
+          <t>复合持续条件规则组 ID；与平铺条件按 AND 合并。不满足时暂停而非移除；0 表示不使用。</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -5119,20 +5119,28 @@
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n"/>
     </row>
@@ -5291,7 +5299,11 @@
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1020</t>
@@ -5302,7 +5314,7 @@
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
@@ -5319,7 +5331,11 @@
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1018</t>
@@ -5330,7 +5346,7 @@
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
@@ -5347,7 +5363,11 @@
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1019</t>
@@ -5358,7 +5378,7 @@
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
@@ -5375,7 +5395,11 @@
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1016</t>
@@ -5386,7 +5410,7 @@
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
@@ -5403,7 +5427,11 @@
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1014</t>
@@ -5414,7 +5442,7 @@
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
@@ -5431,7 +5459,11 @@
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1013</t>
@@ -5442,7 +5474,7 @@
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
@@ -5459,7 +5491,11 @@
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1001,1002</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1015</t>
@@ -5470,7 +5506,7 @@
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>

--- a/LubanConfig/Moba/Production/Datas/J-标签表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-标签表.xlsx
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
